--- a/documentation/metadata.xlsx
+++ b/documentation/metadata.xlsx
@@ -1,22 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dani\Desktop\MASTER\TFM\tfm\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E88FF93-C26F-4935-94F0-D0563691EFA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24ABF6F8-B4A3-4E48-828E-5DBA8165C472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="metadata" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
     </ext>
@@ -1194,9 +1205,6 @@
     <t>https://www.boe.es/eli/es/lo/2018/12/05/3/con</t>
   </si>
   <si>
-    <t>C2|A1|A2</t>
-  </si>
-  <si>
     <t>doc122</t>
   </si>
   <si>
@@ -2236,6 +2244,9 @@
   </si>
   <si>
     <t>https://www.boe.es/eli/es/rd/1983/08/04/2099/con</t>
+  </si>
+  <si>
+    <t>C2|A2</t>
   </si>
 </sst>
 </file>
@@ -2537,7 +2548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F1048576"/>
+  <dimension ref="A1:F236"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5546875" style="1"/>
@@ -3009,7 +3020,7 @@
         <v>89</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>9</v>
+        <v>168</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>10</v>
@@ -3417,7 +3428,7 @@
         <v>155</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>9</v>
+        <v>168</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>10</v>
@@ -3597,7 +3608,7 @@
         <v>183</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>10</v>
@@ -3735,7 +3746,7 @@
         <v>206</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="F61" s="4" t="s">
         <v>10</v>
@@ -4535,7 +4546,7 @@
         <v>328</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>9</v>
+        <v>168</v>
       </c>
       <c r="F101" s="4" t="s">
         <v>10</v>
@@ -4595,7 +4606,7 @@
         <v>337</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="F104" s="4" t="s">
         <v>10</v>
@@ -4795,7 +4806,7 @@
         <v>367</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="F114" s="4" t="s">
         <v>10</v>
@@ -4935,7 +4946,7 @@
         <v>388</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>389</v>
+        <v>63</v>
       </c>
       <c r="F121" s="4" t="s">
         <v>10</v>
@@ -4943,16 +4954,16 @@
     </row>
     <row r="122" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="B122" s="5" t="s">
         <v>390</v>
-      </c>
-      <c r="B122" s="5" t="s">
-        <v>391</v>
       </c>
       <c r="C122" s="6">
         <v>44352</v>
       </c>
       <c r="D122" s="7" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E122" s="4" t="s">
         <v>9</v>
@@ -4963,16 +4974,16 @@
     </row>
     <row r="123" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="B123" s="5" t="s">
         <v>393</v>
-      </c>
-      <c r="B123" s="5" t="s">
-        <v>394</v>
       </c>
       <c r="C123" s="6">
         <v>33962</v>
       </c>
       <c r="D123" s="7" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E123" s="4" t="s">
         <v>9</v>
@@ -4983,16 +4994,16 @@
     </row>
     <row r="124" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="B124" s="5" t="s">
         <v>396</v>
-      </c>
-      <c r="B124" s="5" t="s">
-        <v>397</v>
       </c>
       <c r="C124" s="6">
         <v>45506</v>
       </c>
       <c r="D124" s="7" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E124" s="4" t="s">
         <v>168</v>
@@ -5003,16 +5014,16 @@
     </row>
     <row r="125" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="B125" s="5" t="s">
         <v>399</v>
-      </c>
-      <c r="B125" s="5" t="s">
-        <v>400</v>
       </c>
       <c r="C125" s="6">
         <v>40121</v>
       </c>
       <c r="D125" s="7" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E125" s="4" t="s">
         <v>63</v>
@@ -5023,16 +5034,16 @@
     </row>
     <row r="126" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="B126" s="5" t="s">
         <v>402</v>
-      </c>
-      <c r="B126" s="5" t="s">
-        <v>403</v>
       </c>
       <c r="C126" s="6">
         <v>45705</v>
       </c>
       <c r="D126" s="7" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E126" s="4" t="s">
         <v>63</v>
@@ -5043,16 +5054,16 @@
     </row>
     <row r="127" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="B127" s="5" t="s">
         <v>405</v>
-      </c>
-      <c r="B127" s="5" t="s">
-        <v>406</v>
       </c>
       <c r="C127" s="6">
         <v>46205</v>
       </c>
       <c r="D127" s="7" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E127" s="4" t="s">
         <v>9</v>
@@ -5063,16 +5074,16 @@
     </row>
     <row r="128" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="B128" s="5" t="s">
         <v>408</v>
-      </c>
-      <c r="B128" s="5" t="s">
-        <v>409</v>
       </c>
       <c r="C128" s="6">
         <v>45506</v>
       </c>
       <c r="D128" s="7" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E128" s="4" t="s">
         <v>63</v>
@@ -5083,16 +5094,16 @@
     </row>
     <row r="129" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="B129" s="5" t="s">
         <v>411</v>
-      </c>
-      <c r="B129" s="5" t="s">
-        <v>412</v>
       </c>
       <c r="C129" s="6">
         <v>45506</v>
       </c>
       <c r="D129" s="7" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E129" s="4" t="s">
         <v>51</v>
@@ -5103,16 +5114,16 @@
     </row>
     <row r="130" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="B130" s="5" t="s">
         <v>414</v>
-      </c>
-      <c r="B130" s="5" t="s">
-        <v>415</v>
       </c>
       <c r="C130" s="6">
         <v>45506</v>
       </c>
       <c r="D130" s="7" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E130" s="4" t="s">
         <v>63</v>
@@ -5123,16 +5134,16 @@
     </row>
     <row r="131" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="B131" s="5" t="s">
         <v>417</v>
-      </c>
-      <c r="B131" s="5" t="s">
-        <v>418</v>
       </c>
       <c r="C131" s="6">
         <v>45655</v>
       </c>
       <c r="D131" s="7" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E131" s="4" t="s">
         <v>9</v>
@@ -5143,16 +5154,16 @@
     </row>
     <row r="132" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="B132" s="5" t="s">
         <v>420</v>
-      </c>
-      <c r="B132" s="5" t="s">
-        <v>421</v>
       </c>
       <c r="C132" s="6">
         <v>45836</v>
       </c>
       <c r="D132" s="7" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E132" s="4" t="s">
         <v>9</v>
@@ -5163,16 +5174,16 @@
     </row>
     <row r="133" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="B133" s="5" t="s">
         <v>423</v>
-      </c>
-      <c r="B133" s="5" t="s">
-        <v>424</v>
       </c>
       <c r="C133" s="6">
         <v>41978</v>
       </c>
       <c r="D133" s="7" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E133" s="4" t="s">
         <v>9</v>
@@ -5183,16 +5194,16 @@
     </row>
     <row r="134" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="B134" s="5" t="s">
         <v>426</v>
-      </c>
-      <c r="B134" s="5" t="s">
-        <v>427</v>
       </c>
       <c r="C134" s="6">
         <v>45735</v>
       </c>
       <c r="D134" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E134" s="4" t="s">
         <v>168</v>
@@ -5203,16 +5214,16 @@
     </row>
     <row r="135" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="B135" s="5" t="s">
         <v>429</v>
-      </c>
-      <c r="B135" s="5" t="s">
-        <v>430</v>
       </c>
       <c r="C135" s="6">
         <v>45442</v>
       </c>
       <c r="D135" s="7" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E135" s="4" t="s">
         <v>9</v>
@@ -5223,16 +5234,16 @@
     </row>
     <row r="136" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="B136" s="5" t="s">
         <v>432</v>
-      </c>
-      <c r="B136" s="5" t="s">
-        <v>433</v>
       </c>
       <c r="C136" s="6">
         <v>44986</v>
       </c>
       <c r="D136" s="7" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E136" s="4" t="s">
         <v>18</v>
@@ -5241,16 +5252,16 @@
     </row>
     <row r="137" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="B137" s="5" t="s">
         <v>435</v>
-      </c>
-      <c r="B137" s="5" t="s">
-        <v>436</v>
       </c>
       <c r="C137" s="6">
         <v>43442</v>
       </c>
       <c r="D137" s="7" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E137" s="4" t="s">
         <v>9</v>
@@ -5261,16 +5272,16 @@
     </row>
     <row r="138" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="B138" s="5" t="s">
         <v>438</v>
-      </c>
-      <c r="B138" s="5" t="s">
-        <v>439</v>
       </c>
       <c r="C138" s="6">
         <v>44149</v>
       </c>
       <c r="D138" s="7" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E138" s="4" t="s">
         <v>9</v>
@@ -5281,16 +5292,16 @@
     </row>
     <row r="139" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="B139" s="5" t="s">
         <v>441</v>
-      </c>
-      <c r="B139" s="5" t="s">
-        <v>442</v>
       </c>
       <c r="C139" s="6">
         <v>45568</v>
       </c>
       <c r="D139" s="7" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E139" s="4" t="s">
         <v>63</v>
@@ -5301,36 +5312,36 @@
     </row>
     <row r="140" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="B140" s="5" t="s">
         <v>444</v>
-      </c>
-      <c r="B140" s="5" t="s">
-        <v>445</v>
       </c>
       <c r="C140" s="6">
         <v>46121</v>
       </c>
       <c r="D140" s="7" t="s">
+        <v>445</v>
+      </c>
+      <c r="E140" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F140" s="4" t="s">
         <v>446</v>
-      </c>
-      <c r="E140" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F140" s="4" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="141" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="B141" s="5" t="s">
         <v>448</v>
-      </c>
-      <c r="B141" s="5" t="s">
-        <v>449</v>
       </c>
       <c r="C141" s="6">
         <v>44771</v>
       </c>
       <c r="D141" s="7" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E141" s="4" t="s">
         <v>9</v>
@@ -5341,16 +5352,16 @@
     </row>
     <row r="142" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="B142" s="5" t="s">
         <v>451</v>
-      </c>
-      <c r="B142" s="5" t="s">
-        <v>452</v>
       </c>
       <c r="C142" s="6">
         <v>42195</v>
       </c>
       <c r="D142" s="7" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E142" s="4" t="s">
         <v>9</v>
@@ -5361,16 +5372,16 @@
     </row>
     <row r="143" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="B143" s="5" t="s">
         <v>454</v>
-      </c>
-      <c r="B143" s="5" t="s">
-        <v>455</v>
       </c>
       <c r="C143" s="6">
         <v>35504</v>
       </c>
       <c r="D143" s="7" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E143" s="4" t="s">
         <v>9</v>
@@ -5381,16 +5392,16 @@
     </row>
     <row r="144" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="B144" s="5" t="s">
         <v>457</v>
-      </c>
-      <c r="B144" s="5" t="s">
-        <v>458</v>
       </c>
       <c r="C144" s="6">
         <v>31363</v>
       </c>
       <c r="D144" s="7" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E144" s="4" t="s">
         <v>9</v>
@@ -5401,16 +5412,16 @@
     </row>
     <row r="145" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="B145" s="5" t="s">
         <v>460</v>
-      </c>
-      <c r="B145" s="5" t="s">
-        <v>461</v>
       </c>
       <c r="C145" s="6">
         <v>45055</v>
       </c>
       <c r="D145" s="7" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E145" s="4" t="s">
         <v>9</v>
@@ -5421,16 +5432,16 @@
     </row>
     <row r="146" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="B146" s="5" t="s">
         <v>463</v>
-      </c>
-      <c r="B146" s="5" t="s">
-        <v>464</v>
       </c>
       <c r="C146" s="6">
         <v>45660</v>
       </c>
       <c r="D146" s="7" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E146" s="4" t="s">
         <v>63</v>
@@ -5441,16 +5452,16 @@
     </row>
     <row r="147" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="B147" s="5" t="s">
         <v>466</v>
-      </c>
-      <c r="B147" s="5" t="s">
-        <v>467</v>
       </c>
       <c r="C147" s="6">
         <v>45777</v>
       </c>
       <c r="D147" s="7" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E147" s="4" t="s">
         <v>9</v>
@@ -5461,16 +5472,16 @@
     </row>
     <row r="148" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="B148" s="5" t="s">
         <v>469</v>
-      </c>
-      <c r="B148" s="5" t="s">
-        <v>470</v>
       </c>
       <c r="C148" s="6">
         <v>46176</v>
       </c>
       <c r="D148" s="7" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E148" s="4" t="s">
         <v>63</v>
@@ -5481,16 +5492,16 @@
     </row>
     <row r="149" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="B149" s="5" t="s">
         <v>472</v>
-      </c>
-      <c r="B149" s="5" t="s">
-        <v>473</v>
       </c>
       <c r="C149" s="6">
         <v>44362</v>
       </c>
       <c r="D149" s="7" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E149" s="4" t="s">
         <v>9</v>
@@ -5501,16 +5512,16 @@
     </row>
     <row r="150" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="B150" s="5" t="s">
         <v>475</v>
-      </c>
-      <c r="B150" s="5" t="s">
-        <v>476</v>
       </c>
       <c r="C150" s="6">
         <v>44986</v>
       </c>
       <c r="D150" s="7" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E150" s="4" t="s">
         <v>168</v>
@@ -5521,16 +5532,16 @@
     </row>
     <row r="151" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="B151" s="5" t="s">
         <v>478</v>
-      </c>
-      <c r="B151" s="5" t="s">
-        <v>479</v>
       </c>
       <c r="C151" s="6">
         <v>42094</v>
       </c>
       <c r="D151" s="7" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E151" s="4" t="s">
         <v>9</v>
@@ -5541,16 +5552,16 @@
     </row>
     <row r="152" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="B152" s="5" t="s">
         <v>481</v>
-      </c>
-      <c r="B152" s="5" t="s">
-        <v>482</v>
       </c>
       <c r="C152" s="6">
         <v>44854</v>
       </c>
       <c r="D152" s="7" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E152" s="4" t="s">
         <v>9</v>
@@ -5561,16 +5572,16 @@
     </row>
     <row r="153" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="B153" s="5" t="s">
         <v>484</v>
-      </c>
-      <c r="B153" s="5" t="s">
-        <v>485</v>
       </c>
       <c r="C153" s="6">
         <v>45506</v>
       </c>
       <c r="D153" s="7" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E153" s="4" t="s">
         <v>9</v>
@@ -5581,16 +5592,16 @@
     </row>
     <row r="154" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="B154" s="5" t="s">
         <v>487</v>
-      </c>
-      <c r="B154" s="5" t="s">
-        <v>488</v>
       </c>
       <c r="C154" s="6">
         <v>44147</v>
       </c>
       <c r="D154" s="7" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E154" s="4" t="s">
         <v>9</v>
@@ -5601,16 +5612,16 @@
     </row>
     <row r="155" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="B155" s="5" t="s">
         <v>490</v>
-      </c>
-      <c r="B155" s="5" t="s">
-        <v>491</v>
       </c>
       <c r="C155" s="6">
         <v>44650</v>
       </c>
       <c r="D155" s="7" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E155" s="4" t="s">
         <v>9</v>
@@ -5621,16 +5632,16 @@
     </row>
     <row r="156" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="B156" s="5" t="s">
         <v>493</v>
-      </c>
-      <c r="B156" s="5" t="s">
-        <v>494</v>
       </c>
       <c r="C156" s="6">
         <v>42308</v>
       </c>
       <c r="D156" s="7" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E156" s="4" t="s">
         <v>168</v>
@@ -5641,16 +5652,16 @@
     </row>
     <row r="157" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="B157" s="5" t="s">
         <v>496</v>
-      </c>
-      <c r="B157" s="5" t="s">
-        <v>497</v>
       </c>
       <c r="C157" s="6">
         <v>45055</v>
       </c>
       <c r="D157" s="7" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E157" s="4" t="s">
         <v>244</v>
@@ -5661,19 +5672,19 @@
     </row>
     <row r="158" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="B158" s="5" t="s">
         <v>499</v>
-      </c>
-      <c r="B158" s="5" t="s">
-        <v>500</v>
       </c>
       <c r="C158" s="6">
         <v>39994</v>
       </c>
       <c r="D158" s="7" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="F158" s="4" t="s">
         <v>10</v>
@@ -5681,16 +5692,16 @@
     </row>
     <row r="159" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="B159" s="5" t="s">
         <v>502</v>
-      </c>
-      <c r="B159" s="5" t="s">
-        <v>503</v>
       </c>
       <c r="C159" s="6">
         <v>45574</v>
       </c>
       <c r="D159" s="7" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E159" s="4" t="s">
         <v>18</v>
@@ -5699,16 +5710,16 @@
     </row>
     <row r="160" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="B160" s="5" t="s">
         <v>505</v>
-      </c>
-      <c r="B160" s="5" t="s">
-        <v>506</v>
       </c>
       <c r="C160" s="6">
         <v>43505</v>
       </c>
       <c r="D160" s="7" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E160" s="4" t="s">
         <v>9</v>
@@ -5719,16 +5730,16 @@
     </row>
     <row r="161" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="B161" s="5" t="s">
         <v>508</v>
-      </c>
-      <c r="B161" s="5" t="s">
-        <v>509</v>
       </c>
       <c r="C161" s="6">
         <v>44559</v>
       </c>
       <c r="D161" s="7" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E161" s="4" t="s">
         <v>26</v>
@@ -5737,16 +5748,16 @@
     </row>
     <row r="162" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="B162" s="5" t="s">
         <v>511</v>
-      </c>
-      <c r="B162" s="5" t="s">
-        <v>512</v>
       </c>
       <c r="C162" s="6">
         <v>46102</v>
       </c>
       <c r="D162" s="7" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E162" s="4" t="s">
         <v>9</v>
@@ -5757,16 +5768,16 @@
     </row>
     <row r="163" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="B163" s="5" t="s">
         <v>514</v>
-      </c>
-      <c r="B163" s="5" t="s">
-        <v>515</v>
       </c>
       <c r="C163" s="6">
         <v>32487</v>
       </c>
       <c r="D163" s="7" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E163" s="4" t="s">
         <v>9</v>
@@ -5777,16 +5788,16 @@
     </row>
     <row r="164" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="B164" s="5" t="s">
         <v>517</v>
-      </c>
-      <c r="B164" s="5" t="s">
-        <v>518</v>
       </c>
       <c r="C164" s="6">
         <v>45602</v>
       </c>
       <c r="D164" s="7" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E164" s="4" t="s">
         <v>9</v>
@@ -5797,16 +5808,16 @@
     </row>
     <row r="165" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="B165" s="5" t="s">
         <v>520</v>
-      </c>
-      <c r="B165" s="5" t="s">
-        <v>521</v>
       </c>
       <c r="C165" s="6">
         <v>32683</v>
       </c>
       <c r="D165" s="7" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E165" s="4" t="s">
         <v>26</v>
@@ -5815,16 +5826,16 @@
     </row>
     <row r="166" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="B166" s="5" t="s">
         <v>523</v>
-      </c>
-      <c r="B166" s="5" t="s">
-        <v>524</v>
       </c>
       <c r="C166" s="6">
         <v>45647</v>
       </c>
       <c r="D166" s="7" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E166" s="4" t="s">
         <v>9</v>
@@ -5835,16 +5846,16 @@
     </row>
     <row r="167" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
+        <v>525</v>
+      </c>
+      <c r="B167" s="5" t="s">
         <v>526</v>
-      </c>
-      <c r="B167" s="5" t="s">
-        <v>527</v>
       </c>
       <c r="C167" s="6">
         <v>44560</v>
       </c>
       <c r="D167" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E167" s="4" t="s">
         <v>9</v>
@@ -5855,16 +5866,16 @@
     </row>
     <row r="168" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="B168" s="5" t="s">
         <v>529</v>
-      </c>
-      <c r="B168" s="5" t="s">
-        <v>530</v>
       </c>
       <c r="C168" s="6">
         <v>37064</v>
       </c>
       <c r="D168" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="E168" s="4" t="s">
         <v>67</v>
@@ -5873,16 +5884,16 @@
     </row>
     <row r="169" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="B169" s="5" t="s">
         <v>532</v>
-      </c>
-      <c r="B169" s="5" t="s">
-        <v>533</v>
       </c>
       <c r="C169" s="6">
         <v>41782</v>
       </c>
       <c r="D169" s="7" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E169" s="4" t="s">
         <v>18</v>
@@ -5891,16 +5902,16 @@
     </row>
     <row r="170" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="B170" s="5" t="s">
         <v>535</v>
-      </c>
-      <c r="B170" s="5" t="s">
-        <v>536</v>
       </c>
       <c r="C170" s="6">
         <v>42334</v>
       </c>
       <c r="D170" s="7" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E170" s="4" t="s">
         <v>109</v>
@@ -5909,16 +5920,16 @@
     </row>
     <row r="171" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="B171" s="5" t="s">
         <v>538</v>
-      </c>
-      <c r="B171" s="5" t="s">
-        <v>539</v>
       </c>
       <c r="C171" s="6">
         <v>44919</v>
       </c>
       <c r="D171" s="7" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E171" s="4" t="s">
         <v>9</v>
@@ -5929,16 +5940,16 @@
     </row>
     <row r="172" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="B172" s="5" t="s">
         <v>541</v>
-      </c>
-      <c r="B172" s="5" t="s">
-        <v>542</v>
       </c>
       <c r="C172" s="6">
         <v>44509</v>
       </c>
       <c r="D172" s="7" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E172" s="4" t="s">
         <v>9</v>
@@ -5949,16 +5960,16 @@
     </row>
     <row r="173" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="B173" s="5" t="s">
         <v>544</v>
-      </c>
-      <c r="B173" s="5" t="s">
-        <v>545</v>
       </c>
       <c r="C173" s="6">
         <v>45660</v>
       </c>
       <c r="D173" s="7" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E173" s="4" t="s">
         <v>63</v>
@@ -5969,36 +5980,36 @@
     </row>
     <row r="174" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="B174" s="5" t="s">
         <v>547</v>
-      </c>
-      <c r="B174" s="5" t="s">
-        <v>548</v>
       </c>
       <c r="C174" s="6">
         <v>44615</v>
       </c>
       <c r="D174" s="7" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E174" s="4" t="s">
         <v>9</v>
       </c>
       <c r="F174" s="4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="175" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="B175" s="5" t="s">
         <v>550</v>
-      </c>
-      <c r="B175" s="5" t="s">
-        <v>551</v>
       </c>
       <c r="C175" s="6">
         <v>44738</v>
       </c>
       <c r="D175" s="7" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E175" s="4" t="s">
         <v>9</v>
@@ -6009,16 +6020,16 @@
     </row>
     <row r="176" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="B176" s="5" t="s">
         <v>553</v>
-      </c>
-      <c r="B176" s="5" t="s">
-        <v>554</v>
       </c>
       <c r="C176" s="6">
         <v>45106</v>
       </c>
       <c r="D176" s="7" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="E176" s="4" t="s">
         <v>9</v>
@@ -6029,16 +6040,16 @@
     </row>
     <row r="177" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="B177" s="5" t="s">
         <v>556</v>
-      </c>
-      <c r="B177" s="5" t="s">
-        <v>557</v>
       </c>
       <c r="C177" s="6">
         <v>43442</v>
       </c>
       <c r="D177" s="7" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="E177" s="4" t="s">
         <v>9</v>
@@ -6049,36 +6060,36 @@
     </row>
     <row r="178" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="B178" s="5" t="s">
         <v>559</v>
-      </c>
-      <c r="B178" s="5" t="s">
-        <v>560</v>
       </c>
       <c r="C178" s="6">
         <v>46197</v>
       </c>
       <c r="D178" s="7" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E178" s="4" t="s">
         <v>168</v>
       </c>
       <c r="F178" s="4" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="179" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="B179" s="5" t="s">
         <v>563</v>
-      </c>
-      <c r="B179" s="5" t="s">
-        <v>564</v>
       </c>
       <c r="C179" s="6">
         <v>43774</v>
       </c>
       <c r="D179" s="7" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E179" s="4" t="s">
         <v>9</v>
@@ -6089,16 +6100,16 @@
     </row>
     <row r="180" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
+        <v>565</v>
+      </c>
+      <c r="B180" s="5" t="s">
         <v>566</v>
-      </c>
-      <c r="B180" s="5" t="s">
-        <v>567</v>
       </c>
       <c r="C180" s="6">
         <v>44650</v>
       </c>
       <c r="D180" s="7" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E180" s="4" t="s">
         <v>9</v>
@@ -6109,16 +6120,16 @@
     </row>
     <row r="181" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="B181" s="5" t="s">
         <v>569</v>
-      </c>
-      <c r="B181" s="5" t="s">
-        <v>570</v>
       </c>
       <c r="C181" s="6">
         <v>29701</v>
       </c>
       <c r="D181" s="7" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E181" s="4" t="s">
         <v>168</v>
@@ -6129,16 +6140,16 @@
     </row>
     <row r="182" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="B182" s="5" t="s">
         <v>572</v>
-      </c>
-      <c r="B182" s="5" t="s">
-        <v>573</v>
       </c>
       <c r="C182" s="6">
         <v>44541</v>
       </c>
       <c r="D182" s="7" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E182" s="4" t="s">
         <v>26</v>
@@ -6147,19 +6158,19 @@
     </row>
     <row r="183" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="B183" s="5" t="s">
         <v>575</v>
-      </c>
-      <c r="B183" s="5" t="s">
-        <v>576</v>
       </c>
       <c r="C183" s="6">
         <v>45749</v>
       </c>
       <c r="D183" s="7" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="F183" s="4" t="s">
         <v>10</v>
@@ -6167,16 +6178,16 @@
     </row>
     <row r="184" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="B184" s="5" t="s">
         <v>578</v>
-      </c>
-      <c r="B184" s="5" t="s">
-        <v>579</v>
       </c>
       <c r="C184" s="6">
         <v>31600</v>
       </c>
       <c r="D184" s="7" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E184" s="4" t="s">
         <v>9</v>
@@ -6187,16 +6198,16 @@
     </row>
     <row r="185" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="B185" s="5" t="s">
         <v>581</v>
-      </c>
-      <c r="B185" s="5" t="s">
-        <v>582</v>
       </c>
       <c r="C185" s="6">
         <v>43362</v>
       </c>
       <c r="D185" s="7" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E185" s="4" t="s">
         <v>26</v>
@@ -6205,16 +6216,16 @@
     </row>
     <row r="186" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="B186" s="5" t="s">
         <v>584</v>
-      </c>
-      <c r="B186" s="5" t="s">
-        <v>585</v>
       </c>
       <c r="C186" s="6">
         <v>34046</v>
       </c>
       <c r="D186" s="7" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="E186" s="4" t="s">
         <v>9</v>
@@ -6225,16 +6236,16 @@
     </row>
     <row r="187" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="B187" s="5" t="s">
         <v>587</v>
-      </c>
-      <c r="B187" s="5" t="s">
-        <v>588</v>
       </c>
       <c r="C187" s="6">
         <v>39350</v>
       </c>
       <c r="D187" s="7" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E187" s="4" t="s">
         <v>9</v>
@@ -6245,16 +6256,16 @@
     </row>
     <row r="188" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="B188" s="5" t="s">
         <v>590</v>
-      </c>
-      <c r="B188" s="5" t="s">
-        <v>591</v>
       </c>
       <c r="C188" s="6">
         <v>36470</v>
       </c>
       <c r="D188" s="7" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E188" s="4" t="s">
         <v>168</v>
@@ -6265,16 +6276,16 @@
     </row>
     <row r="189" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="B189" s="5" t="s">
         <v>593</v>
-      </c>
-      <c r="B189" s="5" t="s">
-        <v>594</v>
       </c>
       <c r="C189" s="6">
         <v>45106</v>
       </c>
       <c r="D189" s="7" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E189" s="4" t="s">
         <v>51</v>
@@ -6285,16 +6296,16 @@
     </row>
     <row r="190" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
+        <v>595</v>
+      </c>
+      <c r="B190" s="5" t="s">
         <v>596</v>
-      </c>
-      <c r="B190" s="5" t="s">
-        <v>597</v>
       </c>
       <c r="C190" s="6">
         <v>45021</v>
       </c>
       <c r="D190" s="7" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E190" s="4" t="s">
         <v>9</v>
@@ -6305,16 +6316,16 @@
     </row>
     <row r="191" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="B191" s="5" t="s">
         <v>599</v>
-      </c>
-      <c r="B191" s="5" t="s">
-        <v>600</v>
       </c>
       <c r="C191" s="6">
         <v>45947</v>
       </c>
       <c r="D191" s="7" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E191" s="4" t="s">
         <v>9</v>
@@ -6325,16 +6336,16 @@
     </row>
     <row r="192" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="B192" s="5" t="s">
         <v>602</v>
-      </c>
-      <c r="B192" s="5" t="s">
-        <v>603</v>
       </c>
       <c r="C192" s="6">
         <v>33603</v>
       </c>
       <c r="D192" s="7" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E192" s="4" t="s">
         <v>18</v>
@@ -6343,16 +6354,16 @@
     </row>
     <row r="193" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="B193" s="5" t="s">
         <v>605</v>
-      </c>
-      <c r="B193" s="5" t="s">
-        <v>606</v>
       </c>
       <c r="C193" s="6">
         <v>45588</v>
       </c>
       <c r="D193" s="7" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="E193" s="4" t="s">
         <v>9</v>
@@ -6363,16 +6374,16 @@
     </row>
     <row r="194" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="B194" s="5" t="s">
         <v>608</v>
-      </c>
-      <c r="B194" s="5" t="s">
-        <v>609</v>
       </c>
       <c r="C194" s="6">
         <v>38780</v>
       </c>
       <c r="D194" s="7" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="E194" s="4" t="s">
         <v>63</v>
@@ -6383,16 +6394,16 @@
     </row>
     <row r="195" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="B195" s="5" t="s">
         <v>611</v>
-      </c>
-      <c r="B195" s="5" t="s">
-        <v>612</v>
       </c>
       <c r="C195" s="6">
         <v>45869</v>
       </c>
       <c r="D195" s="7" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="E195" s="4" t="s">
         <v>9</v>
@@ -6403,16 +6414,16 @@
     </row>
     <row r="196" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="B196" s="5" t="s">
         <v>614</v>
-      </c>
-      <c r="B196" s="5" t="s">
-        <v>615</v>
       </c>
       <c r="C196" s="6">
         <v>36543</v>
       </c>
       <c r="D196" s="7" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E196" s="4" t="s">
         <v>63</v>
@@ -6423,16 +6434,16 @@
     </row>
     <row r="197" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="B197" s="5" t="s">
         <v>617</v>
-      </c>
-      <c r="B197" s="5" t="s">
-        <v>618</v>
       </c>
       <c r="C197" s="6">
         <v>42487</v>
       </c>
       <c r="D197" s="7" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="E197" s="4" t="s">
         <v>67</v>
@@ -6441,16 +6452,16 @@
     </row>
     <row r="198" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
+        <v>619</v>
+      </c>
+      <c r="B198" s="5" t="s">
         <v>620</v>
-      </c>
-      <c r="B198" s="5" t="s">
-        <v>621</v>
       </c>
       <c r="C198" s="6">
         <v>38780</v>
       </c>
       <c r="D198" s="7" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="E198" s="4" t="s">
         <v>63</v>
@@ -6461,16 +6472,16 @@
     </row>
     <row r="199" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="B199" s="5" t="s">
         <v>623</v>
-      </c>
-      <c r="B199" s="5" t="s">
-        <v>624</v>
       </c>
       <c r="C199" s="6">
         <v>40074</v>
       </c>
       <c r="D199" s="7" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="E199" s="4" t="s">
         <v>9</v>
@@ -6481,16 +6492,16 @@
     </row>
     <row r="200" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
+        <v>625</v>
+      </c>
+      <c r="B200" s="5" t="s">
         <v>626</v>
-      </c>
-      <c r="B200" s="5" t="s">
-        <v>627</v>
       </c>
       <c r="C200" s="6">
         <v>45647</v>
       </c>
       <c r="D200" s="7" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="E200" s="4" t="s">
         <v>14</v>
@@ -6501,16 +6512,16 @@
     </row>
     <row r="201" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="4" t="s">
+        <v>628</v>
+      </c>
+      <c r="B201" s="5" t="s">
         <v>629</v>
-      </c>
-      <c r="B201" s="5" t="s">
-        <v>630</v>
       </c>
       <c r="C201" s="6">
         <v>46127</v>
       </c>
       <c r="D201" s="7" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="E201" s="4" t="s">
         <v>9</v>
@@ -6521,16 +6532,16 @@
     </row>
     <row r="202" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
+        <v>631</v>
+      </c>
+      <c r="B202" s="5" t="s">
         <v>632</v>
-      </c>
-      <c r="B202" s="5" t="s">
-        <v>633</v>
       </c>
       <c r="C202" s="6">
         <v>38468</v>
       </c>
       <c r="D202" s="7" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="E202" s="4" t="s">
         <v>168</v>
@@ -6541,34 +6552,34 @@
     </row>
     <row r="203" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="B203" s="5" t="s">
         <v>635</v>
-      </c>
-      <c r="B203" s="5" t="s">
-        <v>636</v>
       </c>
       <c r="C203" s="6">
         <v>45412</v>
       </c>
       <c r="D203" s="7" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="E203" s="4" t="s">
-        <v>67</v>
+        <v>736</v>
       </c>
       <c r="F203" s="4"/>
     </row>
     <row r="204" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
+        <v>637</v>
+      </c>
+      <c r="B204" s="5" t="s">
         <v>638</v>
-      </c>
-      <c r="B204" s="5" t="s">
-        <v>639</v>
       </c>
       <c r="C204" s="6">
         <v>45492</v>
       </c>
       <c r="D204" s="7" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="E204" s="4" t="s">
         <v>9</v>
@@ -6579,16 +6590,16 @@
     </row>
     <row r="205" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="4" t="s">
+        <v>640</v>
+      </c>
+      <c r="B205" s="5" t="s">
         <v>641</v>
-      </c>
-      <c r="B205" s="5" t="s">
-        <v>642</v>
       </c>
       <c r="C205" s="6">
         <v>44286</v>
       </c>
       <c r="D205" s="7" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E205" s="4" t="s">
         <v>9</v>
@@ -6599,34 +6610,34 @@
     </row>
     <row r="206" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
+        <v>643</v>
+      </c>
+      <c r="B206" s="5" t="s">
         <v>644</v>
-      </c>
-      <c r="B206" s="5" t="s">
-        <v>645</v>
       </c>
       <c r="C206" s="6">
         <v>40698</v>
       </c>
       <c r="D206" s="7" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="E206" s="4" t="s">
-        <v>109</v>
+        <v>18</v>
       </c>
       <c r="F206" s="4"/>
     </row>
     <row r="207" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="B207" s="5" t="s">
         <v>647</v>
-      </c>
-      <c r="B207" s="5" t="s">
-        <v>648</v>
       </c>
       <c r="C207" s="6">
         <v>44924</v>
       </c>
       <c r="D207" s="7" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E207" s="4" t="s">
         <v>9</v>
@@ -6637,16 +6648,16 @@
     </row>
     <row r="208" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
+        <v>649</v>
+      </c>
+      <c r="B208" s="5" t="s">
         <v>650</v>
-      </c>
-      <c r="B208" s="5" t="s">
-        <v>651</v>
       </c>
       <c r="C208" s="6">
         <v>46072</v>
       </c>
       <c r="D208" s="7" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E208" s="4" t="s">
         <v>9</v>
@@ -6657,16 +6668,16 @@
     </row>
     <row r="209" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="B209" s="5" t="s">
         <v>653</v>
-      </c>
-      <c r="B209" s="5" t="s">
-        <v>654</v>
       </c>
       <c r="C209" s="6">
         <v>45378</v>
       </c>
       <c r="D209" s="7" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="E209" s="4" t="s">
         <v>51</v>
@@ -6677,16 +6688,16 @@
     </row>
     <row r="210" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
+        <v>655</v>
+      </c>
+      <c r="B210" s="5" t="s">
         <v>656</v>
-      </c>
-      <c r="B210" s="5" t="s">
-        <v>657</v>
       </c>
       <c r="C210" s="6">
         <v>43565</v>
       </c>
       <c r="D210" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E210" s="4" t="s">
         <v>26</v>
@@ -6695,16 +6706,16 @@
     </row>
     <row r="211" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="B211" s="5" t="s">
         <v>659</v>
-      </c>
-      <c r="B211" s="5" t="s">
-        <v>660</v>
       </c>
       <c r="C211" s="6">
         <v>35553</v>
       </c>
       <c r="D211" s="7" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E211" s="4" t="s">
         <v>9</v>
@@ -6715,16 +6726,16 @@
     </row>
     <row r="212" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="B212" s="5" t="s">
         <v>662</v>
-      </c>
-      <c r="B212" s="5" t="s">
-        <v>663</v>
       </c>
       <c r="C212" s="6">
         <v>45288</v>
       </c>
       <c r="D212" s="7" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E212" s="4" t="s">
         <v>9</v>
@@ -6735,16 +6746,16 @@
     </row>
     <row r="213" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="4" t="s">
+        <v>664</v>
+      </c>
+      <c r="B213" s="5" t="s">
         <v>665</v>
-      </c>
-      <c r="B213" s="5" t="s">
-        <v>666</v>
       </c>
       <c r="C213" s="6">
         <v>44986</v>
       </c>
       <c r="D213" s="7" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E213" s="4" t="s">
         <v>168</v>
@@ -6755,16 +6766,16 @@
     </row>
     <row r="214" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
+        <v>667</v>
+      </c>
+      <c r="B214" s="5" t="s">
         <v>668</v>
-      </c>
-      <c r="B214" s="5" t="s">
-        <v>669</v>
       </c>
       <c r="C214" s="6">
         <v>44196</v>
       </c>
       <c r="D214" s="7" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="E214" s="4" t="s">
         <v>9</v>
@@ -6775,16 +6786,16 @@
     </row>
     <row r="215" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="4" t="s">
+        <v>670</v>
+      </c>
+      <c r="B215" s="5" t="s">
         <v>671</v>
-      </c>
-      <c r="B215" s="5" t="s">
-        <v>672</v>
       </c>
       <c r="C215" s="6">
         <v>44650</v>
       </c>
       <c r="D215" s="7" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="E215" s="4" t="s">
         <v>9</v>
@@ -6795,16 +6806,16 @@
     </row>
     <row r="216" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="B216" s="5" t="s">
         <v>674</v>
-      </c>
-      <c r="B216" s="5" t="s">
-        <v>675</v>
       </c>
       <c r="C216" s="6">
         <v>45686</v>
       </c>
       <c r="D216" s="7" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="E216" s="4" t="s">
         <v>9</v>
@@ -6815,16 +6826,16 @@
     </row>
     <row r="217" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="4" t="s">
+        <v>676</v>
+      </c>
+      <c r="B217" s="5" t="s">
         <v>677</v>
-      </c>
-      <c r="B217" s="5" t="s">
-        <v>678</v>
       </c>
       <c r="C217" s="6">
         <v>45660</v>
       </c>
       <c r="D217" s="7" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="E217" s="4" t="s">
         <v>9</v>
@@ -6835,16 +6846,16 @@
     </row>
     <row r="218" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="B218" s="5" t="s">
         <v>680</v>
-      </c>
-      <c r="B218" s="5" t="s">
-        <v>681</v>
       </c>
       <c r="C218" s="6">
         <v>45071</v>
       </c>
       <c r="D218" s="7" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="E218" s="4" t="s">
         <v>9</v>
@@ -6855,16 +6866,16 @@
     </row>
     <row r="219" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="4" t="s">
+        <v>682</v>
+      </c>
+      <c r="B219" s="5" t="s">
         <v>683</v>
-      </c>
-      <c r="B219" s="5" t="s">
-        <v>684</v>
       </c>
       <c r="C219" s="6">
         <v>45868</v>
       </c>
       <c r="D219" s="7" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E219" s="4" t="s">
         <v>63</v>
@@ -6875,16 +6886,16 @@
     </row>
     <row r="220" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
+        <v>685</v>
+      </c>
+      <c r="B220" s="5" t="s">
         <v>686</v>
-      </c>
-      <c r="B220" s="5" t="s">
-        <v>687</v>
       </c>
       <c r="C220" s="6">
         <v>45995</v>
       </c>
       <c r="D220" s="7" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="E220" s="4" t="s">
         <v>168</v>
@@ -6895,19 +6906,19 @@
     </row>
     <row r="221" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="4" t="s">
+        <v>688</v>
+      </c>
+      <c r="B221" s="5" t="s">
         <v>689</v>
-      </c>
-      <c r="B221" s="5" t="s">
-        <v>690</v>
       </c>
       <c r="C221" s="6">
         <v>45055</v>
       </c>
       <c r="D221" s="7" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E221" s="4" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="F221" s="4" t="s">
         <v>10</v>
@@ -6915,19 +6926,19 @@
     </row>
     <row r="222" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
+        <v>691</v>
+      </c>
+      <c r="B222" s="5" t="s">
         <v>692</v>
-      </c>
-      <c r="B222" s="5" t="s">
-        <v>693</v>
       </c>
       <c r="C222" s="6">
         <v>46057</v>
       </c>
       <c r="D222" s="7" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E222" s="4" t="s">
-        <v>168</v>
+        <v>14</v>
       </c>
       <c r="F222" s="4" t="s">
         <v>10</v>
@@ -6935,16 +6946,16 @@
     </row>
     <row r="223" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="B223" s="5" t="s">
         <v>695</v>
-      </c>
-      <c r="B223" s="5" t="s">
-        <v>696</v>
       </c>
       <c r="C223" s="6">
         <v>46176</v>
       </c>
       <c r="D223" s="7" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="E223" s="4" t="s">
         <v>9</v>
@@ -6955,16 +6966,16 @@
     </row>
     <row r="224" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
+        <v>697</v>
+      </c>
+      <c r="B224" s="5" t="s">
         <v>698</v>
-      </c>
-      <c r="B224" s="5" t="s">
-        <v>699</v>
       </c>
       <c r="C224" s="6">
         <v>45434</v>
       </c>
       <c r="D224" s="7" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="E224" s="4" t="s">
         <v>9</v>
@@ -6975,19 +6986,19 @@
     </row>
     <row r="225" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="4" t="s">
+        <v>700</v>
+      </c>
+      <c r="B225" s="5" t="s">
         <v>701</v>
-      </c>
-      <c r="B225" s="5" t="s">
-        <v>702</v>
       </c>
       <c r="C225" s="6">
         <v>45647</v>
       </c>
       <c r="D225" s="7" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="E225" s="4" t="s">
-        <v>244</v>
+        <v>63</v>
       </c>
       <c r="F225" s="4" t="s">
         <v>10</v>
@@ -6995,16 +7006,16 @@
     </row>
     <row r="226" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="B226" s="5" t="s">
         <v>704</v>
-      </c>
-      <c r="B226" s="5" t="s">
-        <v>705</v>
       </c>
       <c r="C226" s="6">
         <v>45686</v>
       </c>
       <c r="D226" s="7" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="E226" s="4" t="s">
         <v>9</v>
@@ -7015,16 +7026,16 @@
     </row>
     <row r="227" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="B227" s="5" t="s">
         <v>707</v>
-      </c>
-      <c r="B227" s="5" t="s">
-        <v>708</v>
       </c>
       <c r="C227" s="6">
         <v>45975</v>
       </c>
       <c r="D227" s="7" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="E227" s="4" t="s">
         <v>9</v>
@@ -7035,16 +7046,16 @@
     </row>
     <row r="228" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
+        <v>709</v>
+      </c>
+      <c r="B228" s="5" t="s">
         <v>710</v>
-      </c>
-      <c r="B228" s="5" t="s">
-        <v>711</v>
       </c>
       <c r="C228" s="6">
         <v>43568</v>
       </c>
       <c r="D228" s="7" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E228" s="4" t="s">
         <v>9</v>
@@ -7055,16 +7066,16 @@
     </row>
     <row r="229" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="B229" s="5" t="s">
         <v>713</v>
-      </c>
-      <c r="B229" s="5" t="s">
-        <v>714</v>
       </c>
       <c r="C229" s="6">
         <v>45657</v>
       </c>
       <c r="D229" s="7" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E229" s="4" t="s">
         <v>67</v>
@@ -7073,16 +7084,16 @@
     </row>
     <row r="230" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
+        <v>715</v>
+      </c>
+      <c r="B230" s="5" t="s">
         <v>716</v>
-      </c>
-      <c r="B230" s="5" t="s">
-        <v>717</v>
       </c>
       <c r="C230" s="6">
         <v>32725</v>
       </c>
       <c r="D230" s="7" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="E230" s="4" t="s">
         <v>67</v>
@@ -7091,16 +7102,16 @@
     </row>
     <row r="231" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="4" t="s">
+        <v>718</v>
+      </c>
+      <c r="B231" s="5" t="s">
         <v>719</v>
-      </c>
-      <c r="B231" s="5" t="s">
-        <v>720</v>
       </c>
       <c r="C231" s="6">
         <v>42061</v>
       </c>
       <c r="D231" s="7" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="E231" s="4" t="s">
         <v>67</v>
@@ -7109,16 +7120,16 @@
     </row>
     <row r="232" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="B232" s="5" t="s">
         <v>722</v>
-      </c>
-      <c r="B232" s="5" t="s">
-        <v>723</v>
       </c>
       <c r="C232" s="6">
         <v>44986</v>
       </c>
       <c r="D232" s="7" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="E232" s="4" t="s">
         <v>9</v>
@@ -7129,16 +7140,16 @@
     </row>
     <row r="233" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="4" t="s">
+        <v>724</v>
+      </c>
+      <c r="B233" s="5" t="s">
         <v>725</v>
-      </c>
-      <c r="B233" s="5" t="s">
-        <v>726</v>
       </c>
       <c r="C233" s="6">
         <v>45280</v>
       </c>
       <c r="D233" s="7" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="E233" s="4" t="s">
         <v>9</v>
@@ -7149,16 +7160,16 @@
     </row>
     <row r="234" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
+        <v>727</v>
+      </c>
+      <c r="B234" s="5" t="s">
         <v>728</v>
-      </c>
-      <c r="B234" s="5" t="s">
-        <v>729</v>
       </c>
       <c r="C234" s="6">
         <v>44408</v>
       </c>
       <c r="D234" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E234" s="4" t="s">
         <v>9</v>
@@ -7169,16 +7180,16 @@
     </row>
     <row r="235" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="4" t="s">
+        <v>730</v>
+      </c>
+      <c r="B235" s="5" t="s">
         <v>731</v>
-      </c>
-      <c r="B235" s="5" t="s">
-        <v>732</v>
       </c>
       <c r="C235" s="6">
         <v>28951</v>
       </c>
       <c r="D235" s="7" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E235" s="4" t="s">
         <v>9</v>
@@ -7189,16 +7200,16 @@
     </row>
     <row r="236" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
+        <v>733</v>
+      </c>
+      <c r="B236" s="5" t="s">
         <v>734</v>
-      </c>
-      <c r="B236" s="5" t="s">
-        <v>735</v>
       </c>
       <c r="C236" s="6">
         <v>41809</v>
       </c>
       <c r="D236" s="7" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="E236" s="4" t="s">
         <v>9</v>
@@ -7207,11 +7218,6 @@
         <v>52</v>
       </c>
     </row>
-    <row r="1048572" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1048573" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1048574" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1048575" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1048576" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <conditionalFormatting sqref="B1:B1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
